--- a/data/trans_orig/P2C_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140673</t>
+          <t>140777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181613</t>
+          <t>180975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96480</t>
+          <t>95830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129250</t>
+          <t>130077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247850</t>
+          <t>247181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301283</t>
+          <t>301067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292163</t>
+          <t>292801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>333103</t>
+          <t>332999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177430</t>
+          <t>176603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210200</t>
+          <t>210850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479174</t>
+          <t>479390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532607</t>
+          <t>533276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>90216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126717</t>
+          <t>125081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130983</t>
+          <t>130958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167912</t>
+          <t>169327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232748</t>
+          <t>231305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284297</t>
+          <t>284448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240217</t>
+          <t>241853</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277061</t>
+          <t>276718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203953</t>
+          <t>202538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240882</t>
+          <t>240907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454502</t>
+          <t>454351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506051</t>
+          <t>507494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145832</t>
+          <t>146197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191175</t>
+          <t>191040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>62059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88744</t>
+          <t>89264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219641</t>
+          <t>218690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268467</t>
+          <t>270673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>351214</t>
+          <t>351349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>396557</t>
+          <t>396192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>105723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>441704</t>
+          <t>439498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>490530</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332326</t>
+          <t>329540</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395448</t>
+          <t>395066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252060</t>
+          <t>248464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302601</t>
+          <t>302575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>596427</t>
+          <t>597340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>681636</t>
+          <t>683598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842886</t>
+          <t>843268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>906008</t>
+          <t>908794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411684</t>
+          <t>411710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>462225</t>
+          <t>465821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270984</t>
+          <t>1269022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1356193</t>
+          <t>1355280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87498</t>
+          <t>85821</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121843</t>
+          <t>120839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193311</t>
+          <t>195564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240826</t>
+          <t>238784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>289400</t>
+          <t>292203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>346197</t>
+          <t>348119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228712</t>
+          <t>229716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263057</t>
+          <t>264734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327926</t>
+          <t>329968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375441</t>
+          <t>373188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>573110</t>
+          <t>571188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>629907</t>
+          <t>627104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>41633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66566</t>
+          <t>67672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>306756</t>
+          <t>304259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>369973</t>
+          <t>367840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>351974</t>
+          <t>356569</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>424439</t>
+          <t>426117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231635</t>
+          <t>230529</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258132</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>878787</t>
+          <t>880920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>942004</t>
+          <t>944501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1122521</t>
+          <t>1120843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1194986</t>
+          <t>1190391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>899968</t>
+          <t>900843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1006928</t>
+          <t>1009402</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1111182</t>
+          <t>1113919</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1219543</t>
+          <t>1222996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2039989</t>
+          <t>2048498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2194806</t>
+          <t>2200022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2263262</t>
+          <t>2260788</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2370222</t>
+          <t>2369347</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2158581</t>
+          <t>2155128</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2266942</t>
+          <t>2264205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4453508</t>
+          <t>4448292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4608325</t>
+          <t>4599816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168158</t>
+          <t>171636</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214332</t>
+          <t>213737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150381</t>
+          <t>151580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187766</t>
+          <t>188901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>329716</t>
+          <t>334642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>387859</t>
+          <t>390319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222879</t>
+          <t>223474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269053</t>
+          <t>265575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126688</t>
+          <t>125553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164073</t>
+          <t>162874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>363806</t>
+          <t>361346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>421949</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170131</t>
+          <t>168124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215465</t>
+          <t>213333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189413</t>
+          <t>190647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227207</t>
+          <t>228407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373204</t>
+          <t>370588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>430965</t>
+          <t>431150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203332</t>
+          <t>205464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248666</t>
+          <t>250673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110804</t>
+          <t>109604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>148598</t>
+          <t>147364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325843</t>
+          <t>325658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>383604</t>
+          <t>386220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258087</t>
+          <t>260148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>308960</t>
+          <t>309055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112840</t>
+          <t>113016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145407</t>
+          <t>144329</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384297</t>
+          <t>382683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>444936</t>
+          <t>442310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320455</t>
+          <t>320360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>371328</t>
+          <t>369267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>115800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147289</t>
+          <t>147113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444608</t>
+          <t>447234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505247</t>
+          <t>506861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>520805</t>
+          <t>520253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>596972</t>
+          <t>594426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>406357</t>
+          <t>407288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>464142</t>
+          <t>464595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>950788</t>
+          <t>951408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1044236</t>
+          <t>1041032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562037</t>
+          <t>564583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638204</t>
+          <t>638756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302515</t>
+          <t>302062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360300</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>881431</t>
+          <t>884635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>974879</t>
+          <t>974259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199007</t>
+          <t>199635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245465</t>
+          <t>246559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>401314</t>
+          <t>396902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>455851</t>
+          <t>455426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>613047</t>
+          <t>616200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>689365</t>
+          <t>683814</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>265131</t>
+          <t>264037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311589</t>
+          <t>310961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>305671</t>
+          <t>306096</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360208</t>
+          <t>364620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>582753</t>
+          <t>588304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>659071</t>
+          <t>655918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70398</t>
+          <t>69585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98450</t>
+          <t>100389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>426132</t>
+          <t>428624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>492887</t>
+          <t>492600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>507822</t>
+          <t>508211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>581628</t>
+          <t>583243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168432</t>
+          <t>166493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196484</t>
+          <t>197297</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>616464</t>
+          <t>616751</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>683219</t>
+          <t>680727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>794605</t>
+          <t>792990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>868411</t>
+          <t>868022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1480051</t>
+          <t>1475231</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1594496</t>
+          <t>1597576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1771192</t>
+          <t>1775396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1890883</t>
+          <t>1897766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3280019</t>
+          <t>3278389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3449163</t>
+          <t>3453671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1827414</t>
+          <t>1824334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1941859</t>
+          <t>1946679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1659242</t>
+          <t>1652359</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1778933</t>
+          <t>1774729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3522872</t>
+          <t>3518364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3692016</t>
+          <t>3693646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94469</t>
+          <t>94632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132442</t>
+          <t>132765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130314</t>
+          <t>132369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167105</t>
+          <t>168329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235630</t>
+          <t>233957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>289601</t>
+          <t>290261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296650</t>
+          <t>296327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334623</t>
+          <t>334460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179950</t>
+          <t>178726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216741</t>
+          <t>214686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486546</t>
+          <t>485886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540517</t>
+          <t>542190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123153</t>
+          <t>124901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161608</t>
+          <t>165475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162632</t>
+          <t>160173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201312</t>
+          <t>200417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295790</t>
+          <t>298123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352012</t>
+          <t>353418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215619</t>
+          <t>211752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254074</t>
+          <t>252326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170961</t>
+          <t>171856</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209641</t>
+          <t>212100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397488</t>
+          <t>396082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453710</t>
+          <t>451377</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152296</t>
+          <t>153798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195529</t>
+          <t>196259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54589</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>80213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214341</t>
+          <t>216708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266221</t>
+          <t>264855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326385</t>
+          <t>325655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>369618</t>
+          <t>368116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111534</t>
+          <t>111183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>421815</t>
+          <t>423181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473695</t>
+          <t>471328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327232</t>
+          <t>332299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>393825</t>
+          <t>395241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>329915</t>
+          <t>328882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386526</t>
+          <t>386072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>683929</t>
+          <t>682680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>769002</t>
+          <t>768432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>755813</t>
+          <t>754397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>822406</t>
+          <t>817339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439350</t>
+          <t>439804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>495961</t>
+          <t>496994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1206512</t>
+          <t>1207082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1291585</t>
+          <t>1292834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182394</t>
+          <t>181760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231024</t>
+          <t>228662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274295</t>
+          <t>271884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>324720</t>
+          <t>329628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>472378</t>
+          <t>468051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>545592</t>
+          <t>538984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389682</t>
+          <t>392044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438312</t>
+          <t>438946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>413524</t>
+          <t>408616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>463949</t>
+          <t>466360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813358</t>
+          <t>819966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>886572</t>
+          <t>890899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78339</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>283903</t>
+          <t>278291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343176</t>
+          <t>343050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>340636</t>
+          <t>340480</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408454</t>
+          <t>409145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208806</t>
+          <t>208678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239009</t>
+          <t>237726</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>738849</t>
+          <t>738975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>798122</t>
+          <t>803734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>960716</t>
+          <t>960025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1028534</t>
+          <t>1028690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1005686</t>
+          <t>1008464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1111754</t>
+          <t>1119660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1302001</t>
+          <t>1308397</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1429607</t>
+          <t>1426190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2345902</t>
+          <t>2346160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2508417</t>
+          <t>2506766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2273968</t>
+          <t>2266062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2380036</t>
+          <t>2377258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2101989</t>
+          <t>2105406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2229595</t>
+          <t>2223199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4408901</t>
+          <t>4410552</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4571416</t>
+          <t>4571158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>69078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50936</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75914</t>
+          <t>75496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95669</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133355</t>
+          <t>134239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>435042</t>
+          <t>436134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464776</t>
+          <t>465052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>371553</t>
+          <t>371971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>396531</t>
+          <t>397428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>819324</t>
+          <t>818440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>857010</t>
+          <t>856377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>31075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56409</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68426</t>
+          <t>67695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83396</t>
+          <t>81713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119536</t>
+          <t>115357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395804</t>
+          <t>395481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420378</t>
+          <t>421138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314154</t>
+          <t>314885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337726</t>
+          <t>337751</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715257</t>
+          <t>719436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751397</t>
+          <t>753080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116634</t>
+          <t>115710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28872</t>
+          <t>30125</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135876</t>
+          <t>135006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>551630</t>
+          <t>552554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643046</t>
+          <t>643831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138039</t>
+          <t>136786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151329</t>
+          <t>150896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>699299</t>
+          <t>700169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>796812</t>
+          <t>795939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132039</t>
+          <t>132599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177847</t>
+          <t>180782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143221</t>
+          <t>144443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>638521</t>
+          <t>582607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293923</t>
+          <t>296101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>900493</t>
+          <t>978247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>856972</t>
+          <t>854037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902780</t>
+          <t>902220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339573</t>
+          <t>395487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>834873</t>
+          <t>833651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1112419</t>
+          <t>1034665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1718989</t>
+          <t>1716811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>47545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75742</t>
+          <t>75657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115369</t>
+          <t>111290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179737</t>
+          <t>178972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173968</t>
+          <t>175668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241452</t>
+          <t>242517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399304</t>
+          <t>399389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428453</t>
+          <t>427501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>661598</t>
+          <t>662363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>725966</t>
+          <t>730045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1074929</t>
+          <t>1073864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1142413</t>
+          <t>1140713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30073</t>
+          <t>32131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>149612</t>
+          <t>147312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188716</t>
+          <t>187978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>161185</t>
+          <t>162986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206970</t>
+          <t>209543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210434</t>
+          <t>208376</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232036</t>
+          <t>231911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>572655</t>
+          <t>573393</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>611759</t>
+          <t>614059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>794908</t>
+          <t>792335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>840693</t>
+          <t>838892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>305641</t>
+          <t>310855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>447149</t>
+          <t>447554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>594811</t>
+          <t>595772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1295902</t>
+          <t>1304601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>973764</t>
+          <t>973280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1739777</t>
+          <t>1788773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2928911</t>
+          <t>2928506</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3070419</t>
+          <t>3065205</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2281856</t>
+          <t>2273157</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2982947</t>
+          <t>2981986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5214041</t>
+          <t>5165045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5980054</t>
+          <t>5980538</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140777</t>
+          <t>141516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180975</t>
+          <t>183673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95830</t>
+          <t>95620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130077</t>
+          <t>129172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247181</t>
+          <t>245226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301067</t>
+          <t>302245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292801</t>
+          <t>290103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332999</t>
+          <t>332260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176603</t>
+          <t>177508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210850</t>
+          <t>211060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479390</t>
+          <t>478212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533276</t>
+          <t>535231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90216</t>
+          <t>91211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125081</t>
+          <t>126111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130958</t>
+          <t>131809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169327</t>
+          <t>168994</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231305</t>
+          <t>230812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284448</t>
+          <t>285151</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241853</t>
+          <t>240823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>276718</t>
+          <t>275723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202538</t>
+          <t>202871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240907</t>
+          <t>240056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454351</t>
+          <t>453648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>507494</t>
+          <t>507987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146197</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191040</t>
+          <t>190954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>62645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89264</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218690</t>
+          <t>219825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270673</t>
+          <t>269505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>351349</t>
+          <t>351435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>396192</t>
+          <t>396491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>80581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105723</t>
+          <t>105137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439498</t>
+          <t>440666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491481</t>
+          <t>490346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>329540</t>
+          <t>330707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395066</t>
+          <t>396502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302575</t>
+          <t>300908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>597340</t>
+          <t>592330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>683598</t>
+          <t>673785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>843268</t>
+          <t>841832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908794</t>
+          <t>907627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411710</t>
+          <t>413377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465821</t>
+          <t>466053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1269022</t>
+          <t>1278835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1355280</t>
+          <t>1360290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85821</t>
+          <t>85470</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120839</t>
+          <t>120971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195564</t>
+          <t>191660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238784</t>
+          <t>238822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>292203</t>
+          <t>286692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348119</t>
+          <t>347085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>229716</t>
+          <t>229584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264734</t>
+          <t>265085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>329968</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373188</t>
+          <t>377092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>571188</t>
+          <t>572222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>627104</t>
+          <t>632615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>66235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304259</t>
+          <t>306874</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>367840</t>
+          <t>369784</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>356569</t>
+          <t>358463</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>426117</t>
+          <t>424123</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230529</t>
+          <t>231966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256568</t>
+          <t>257839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>880920</t>
+          <t>878976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>944501</t>
+          <t>941886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1120843</t>
+          <t>1122837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1190391</t>
+          <t>1188497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>900843</t>
+          <t>905133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1009402</t>
+          <t>1007832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1113919</t>
+          <t>1112873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1222996</t>
+          <t>1223247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2048498</t>
+          <t>2048305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2200022</t>
+          <t>2193533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2260788</t>
+          <t>2262358</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2369347</t>
+          <t>2365057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2155128</t>
+          <t>2154877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2264205</t>
+          <t>2265251</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4448292</t>
+          <t>4454781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4599816</t>
+          <t>4600009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171636</t>
+          <t>168848</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213737</t>
+          <t>213208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151580</t>
+          <t>150728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188901</t>
+          <t>189078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,47 +3418,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>47,93%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>60,13%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>362288</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>335767</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>392860</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>48,2%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>60,07%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>362288</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>334642</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>390319</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>48,2%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223474</t>
+          <t>224003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265575</t>
+          <t>268363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>125376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162874</t>
+          <t>163726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,47 +3531,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>52,07%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>389377</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>358805</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>415898</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>51,8%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>389377</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>361346</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>417023</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>51,8%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,33%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168124</t>
+          <t>168998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213333</t>
+          <t>215326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>189889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228407</t>
+          <t>227831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370588</t>
+          <t>371763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>431150</t>
+          <t>430261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205464</t>
+          <t>203471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250673</t>
+          <t>249799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109604</t>
+          <t>110180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147364</t>
+          <t>148122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>325658</t>
+          <t>326547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>386220</t>
+          <t>385045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>260148</t>
+          <t>260388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>309055</t>
+          <t>311383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113016</t>
+          <t>110349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144329</t>
+          <t>144522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>382683</t>
+          <t>384873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>442310</t>
+          <t>450745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320360</t>
+          <t>318032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>369267</t>
+          <t>369027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115800</t>
+          <t>115607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147113</t>
+          <t>149780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447234</t>
+          <t>438799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>506861</t>
+          <t>504671</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>520253</t>
+          <t>523997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>594426</t>
+          <t>597273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>407288</t>
+          <t>409811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>464595</t>
+          <t>468236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>951408</t>
+          <t>951497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1041032</t>
+          <t>1038259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>564583</t>
+          <t>561736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638756</t>
+          <t>635012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302062</t>
+          <t>298421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359369</t>
+          <t>356846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>884635</t>
+          <t>887408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>974259</t>
+          <t>974170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>199635</t>
+          <t>198398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>246559</t>
+          <t>244044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396902</t>
+          <t>398709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>455426</t>
+          <t>453186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>616200</t>
+          <t>610976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>683814</t>
+          <t>684668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264037</t>
+          <t>266552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>310961</t>
+          <t>312198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306096</t>
+          <t>308336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364620</t>
+          <t>362813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>588304</t>
+          <t>587450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>655918</t>
+          <t>661142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69585</t>
+          <t>69531</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100389</t>
+          <t>97720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>428624</t>
+          <t>426146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>492600</t>
+          <t>492773</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>508211</t>
+          <t>511606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>583243</t>
+          <t>583668</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197297</t>
+          <t>197351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>616751</t>
+          <t>616578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>680727</t>
+          <t>683205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>792990</t>
+          <t>792565</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>868022</t>
+          <t>864627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1475231</t>
+          <t>1474755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1597576</t>
+          <t>1591917</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1775396</t>
+          <t>1769519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1897766</t>
+          <t>1891081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3278389</t>
+          <t>3276407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3453671</t>
+          <t>3451505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1824334</t>
+          <t>1829993</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1946679</t>
+          <t>1947155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1652359</t>
+          <t>1659044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1774729</t>
+          <t>1780606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3518364</t>
+          <t>3520530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3693646</t>
+          <t>3695628</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94632</t>
+          <t>95142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132765</t>
+          <t>133400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132369</t>
+          <t>131190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168329</t>
+          <t>168265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233957</t>
+          <t>233433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>290261</t>
+          <t>288320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296327</t>
+          <t>295692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334460</t>
+          <t>333950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178726</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214686</t>
+          <t>215865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485886</t>
+          <t>487827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>542190</t>
+          <t>542714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124901</t>
+          <t>123401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165475</t>
+          <t>163915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160173</t>
+          <t>161815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200417</t>
+          <t>199421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>298123</t>
+          <t>295834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353418</t>
+          <t>352446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211752</t>
+          <t>213312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252326</t>
+          <t>253826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171856</t>
+          <t>172852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212100</t>
+          <t>210458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396082</t>
+          <t>397054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451377</t>
+          <t>453666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153798</t>
+          <t>153878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196259</t>
+          <t>195177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80213</t>
+          <t>80035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216708</t>
+          <t>215440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264855</t>
+          <t>267322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325655</t>
+          <t>326737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>368116</t>
+          <t>368036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85910</t>
+          <t>86088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111183</t>
+          <t>111750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>423181</t>
+          <t>420714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>471328</t>
+          <t>472596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332299</t>
+          <t>335852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395241</t>
+          <t>397746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>328882</t>
+          <t>328777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386072</t>
+          <t>388213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>682680</t>
+          <t>677401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>768432</t>
+          <t>763933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754397</t>
+          <t>751892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>817339</t>
+          <t>813786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>439804</t>
+          <t>437663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496994</t>
+          <t>497099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207082</t>
+          <t>1211581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292834</t>
+          <t>1298113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181760</t>
+          <t>181956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228662</t>
+          <t>231695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>271884</t>
+          <t>275634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329628</t>
+          <t>330426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>468051</t>
+          <t>471898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>538984</t>
+          <t>542849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>392044</t>
+          <t>389011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438946</t>
+          <t>438750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408616</t>
+          <t>407818</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>466360</t>
+          <t>462610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>819966</t>
+          <t>816101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890899</t>
+          <t>887052</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49419</t>
+          <t>50133</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78467</t>
+          <t>78996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>278291</t>
+          <t>282439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343050</t>
+          <t>343668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>340480</t>
+          <t>342213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>409145</t>
+          <t>406125</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208678</t>
+          <t>208149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>237012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>738975</t>
+          <t>738357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>803734</t>
+          <t>799586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>960025</t>
+          <t>963045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1028690</t>
+          <t>1026957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1008464</t>
+          <t>1007889</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1119660</t>
+          <t>1117894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1308397</t>
+          <t>1313048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1426190</t>
+          <t>1431865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2346160</t>
+          <t>2346467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2506766</t>
+          <t>2505460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2266062</t>
+          <t>2267828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2377258</t>
+          <t>2377833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2105406</t>
+          <t>2099731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2223199</t>
+          <t>2218548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4410552</t>
+          <t>4411858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4571158</t>
+          <t>4570851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53166</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>45869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69078</t>
+          <t>78482</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>60783</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75496</t>
+          <t>81370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>113949</t>
+          <t>128014</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96302</t>
+          <t>110057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134239</t>
+          <t>150423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>452046</t>
+          <t>489888</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436134</t>
+          <t>472136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465052</t>
+          <t>504749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>386684</t>
+          <t>421127</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>371971</t>
+          <t>407041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397428</t>
+          <t>434208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>838730</t>
+          <t>911015</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>818440</t>
+          <t>888606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>856377</t>
+          <t>928972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56077</t>
+          <t>63135</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>77254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98801</t>
+          <t>111854</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81713</t>
+          <t>94345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115357</t>
+          <t>131390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>409489</t>
+          <t>434493</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>395481</t>
+          <t>418331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421138</t>
+          <t>447613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>326503</t>
+          <t>360008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314885</t>
+          <t>345889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337751</t>
+          <t>371765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>735992</t>
+          <t>794501</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719436</t>
+          <t>774965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753080</t>
+          <t>812010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>81332</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>65882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115710</t>
+          <t>100368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>105537</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>88426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135006</t>
+          <t>125922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>599211</t>
+          <t>390280</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>552554</t>
+          <t>371244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643831</t>
+          <t>405730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>144790</t>
+          <t>163292</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136786</t>
+          <t>155086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150896</t>
+          <t>169612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>744001</t>
+          <t>553572</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>700169</t>
+          <t>533187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>795939</t>
+          <t>570683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>155024</t>
+          <t>181349</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132599</t>
+          <t>158328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180782</t>
+          <t>208218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>324167</t>
+          <t>135029</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>144443</t>
+          <t>116177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>582607</t>
+          <t>153976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>479191</t>
+          <t>316379</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296101</t>
+          <t>286969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>978247</t>
+          <t>350910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879795</t>
+          <t>950494</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>854037</t>
+          <t>923625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902220</t>
+          <t>973515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>653927</t>
+          <t>726182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>395487</t>
+          <t>707235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>833651</t>
+          <t>745034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1533721</t>
+          <t>1676675</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1034665</t>
+          <t>1642144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1716811</t>
+          <t>1706085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,102 +10005,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47545</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75657</t>
+          <t>84185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>178341</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>159193</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199039</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>246843</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>222799</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>273003</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>15,93%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>152533</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>111290</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>178972</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>213086</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>175668</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>242517</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -10118,102 +10118,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>414493</t>
+          <t>499462</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399389</t>
+          <t>483779</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427501</t>
+          <t>514162</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>652509</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>631811</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>671657</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>76,04%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>80,84%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1151971</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1125811</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1176015</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>84,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>688802</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>662363</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>730045</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,87%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>78,73%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1103295</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1073864</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1140713</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32131</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>167729</t>
+          <t>191707</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147312</t>
+          <t>171020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>187978</t>
+          <t>214539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>184010</t>
+          <t>214224</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162986</t>
+          <t>188537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209543</t>
+          <t>240136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>224226</t>
+          <t>214711</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208376</t>
+          <t>199148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231911</t>
+          <t>224815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>593642</t>
+          <t>652574</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>573393</t>
+          <t>629742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>614059</t>
+          <t>673261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>817868</t>
+          <t>867285</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>792335</t>
+          <t>841373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>838892</t>
+          <t>892972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,57%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>396800</t>
+          <t>463149</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>310855</t>
+          <t>420949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>447554</t>
+          <t>506225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>783411</t>
+          <t>659701</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>595772</t>
+          <t>615254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1304601</t>
+          <t>699844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1180211</t>
+          <t>1122851</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>973280</t>
+          <t>1064310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1788773</t>
+          <t>1182202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2979260</t>
+          <t>2979327</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2928506</t>
+          <t>2936251</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3065205</t>
+          <t>3021527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2794347</t>
+          <t>2975692</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2273157</t>
+          <t>2935549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2981986</t>
+          <t>3020139</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5773607</t>
+          <t>5955018</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5165045</t>
+          <t>5895667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5980538</t>
+          <t>6013559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
